--- a/excel2template/RDEDatasetTemplateSheet_20251222_sample.xlsx
+++ b/excel2template/RDEDatasetTemplateSheet_20251222_sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nims_tosaka/Documents/RDE/gitlab/rde_template_tools/excel2template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdag02\Documents\tosaka\wsl\gitlab\rde_template_tools\excel2template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7900B920-D5E7-6048-B880-87075DC03B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A945422-89AB-491F-93B3-489DA3511D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42780" yWindow="1540" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29700" yWindow="405" windowWidth="20880" windowHeight="13905" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="説明" sheetId="13" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2580" uniqueCount="1496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="1495">
   <si>
     <t>category</t>
     <phoneticPr fontId="2"/>
@@ -5178,10 +5178,6 @@
     <rPh sb="0" eb="2">
       <t xml:space="preserve">ソクテイ </t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ß</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -5508,7 +5504,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5616,6 +5612,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6343,9 +6340,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{262A4EBA-5223-4569-A9B8-7F66B093A1B9}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="59.5" customWidth="1"/>
     <col min="3" max="3" width="42.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -6361,7 +6358,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>1385</v>
       </c>
@@ -6372,7 +6369,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>1386</v>
       </c>
@@ -6392,7 +6389,7 @@
       </c>
       <c r="C4" s="31"/>
     </row>
-    <row r="5" spans="1:3" ht="18">
+    <row r="5" spans="1:3">
       <c r="A5" s="30"/>
     </row>
     <row r="6" spans="1:3">
@@ -6436,8 +6433,8 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" thickBot="1"/>
-    <row r="16" spans="1:3" ht="18" thickTop="1">
+    <row r="15" spans="1:3" ht="19.5" thickBot="1"/>
+    <row r="16" spans="1:3" ht="19.5" thickTop="1">
       <c r="A16" s="40" t="s">
         <v>1452</v>
       </c>
@@ -6539,13 +6536,13 @@
       </c>
       <c r="B34" s="43"/>
     </row>
-    <row r="35" spans="1:2" ht="18" thickBot="1">
+    <row r="35" spans="1:2" ht="19.5" thickBot="1">
       <c r="A35" s="47" t="s">
         <v>1465</v>
       </c>
       <c r="B35" s="48"/>
     </row>
-    <row r="36" spans="1:2" ht="18" thickTop="1"/>
+    <row r="36" spans="1:2" ht="19.5" thickTop="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="B1:B3">
@@ -6571,26 +6568,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A61A9FF-3E2A-4816-B225-73A91309AAFB}">
   <dimension ref="A1:S44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="65.1640625" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="6" width="31.1640625" customWidth="1"/>
-    <col min="7" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.125" customWidth="1"/>
+    <col min="4" max="4" width="14.875" customWidth="1"/>
+    <col min="5" max="6" width="31.125" customWidth="1"/>
+    <col min="7" max="7" width="29.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="55.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.5" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" customWidth="1"/>
-    <col min="14" max="14" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.375" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="14" max="14" width="14.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19.5" customWidth="1"/>
-    <col min="16" max="16" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.1640625" customWidth="1"/>
+    <col min="16" max="16" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
     <col min="18" max="18" width="12.5" customWidth="1"/>
-    <col min="19" max="19" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="49.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -6712,7 +6709,7 @@
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="52" t="s">
         <v>1427</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -6755,7 +6752,7 @@
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="52"/>
+      <c r="A4" s="53"/>
       <c r="B4" s="4" t="s">
         <v>1402</v>
       </c>
@@ -6796,7 +6793,7 @@
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="52"/>
+      <c r="A5" s="53"/>
       <c r="B5" s="4" t="s">
         <v>1402</v>
       </c>
@@ -6839,7 +6836,7 @@
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="52"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="4" t="s">
         <v>1402</v>
       </c>
@@ -6882,7 +6879,7 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="52"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="4" t="s">
         <v>44</v>
       </c>
@@ -6919,7 +6916,7 @@
       <c r="S7" s="9"/>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="52"/>
+      <c r="A8" s="53"/>
       <c r="B8" s="4" t="s">
         <v>44</v>
       </c>
@@ -6950,7 +6947,7 @@
       <c r="S8" s="9"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="52"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="4" t="s">
         <v>44</v>
       </c>
@@ -6981,7 +6978,7 @@
       <c r="S9" s="9"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="52"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="4" t="s">
         <v>44</v>
       </c>
@@ -7012,7 +7009,7 @@
       <c r="S10" s="9"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="52"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="4" t="s">
         <v>44</v>
       </c>
@@ -7043,7 +7040,7 @@
       <c r="S11" s="9"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="52"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="4" t="s">
         <v>44</v>
       </c>
@@ -7074,7 +7071,7 @@
       <c r="S12" s="9"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="52"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="4" t="s">
         <v>44</v>
       </c>
@@ -7105,7 +7102,7 @@
       <c r="S13" s="9"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="52"/>
+      <c r="A14" s="53"/>
       <c r="B14" s="4" t="s">
         <v>44</v>
       </c>
@@ -7136,7 +7133,7 @@
       <c r="S14" s="9"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="52"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="4" t="s">
         <v>44</v>
       </c>
@@ -7167,7 +7164,7 @@
       <c r="S15" s="9"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="52"/>
+      <c r="A16" s="53"/>
       <c r="B16" s="4" t="s">
         <v>44</v>
       </c>
@@ -7198,7 +7195,7 @@
       <c r="S16" s="9"/>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="52"/>
+      <c r="A17" s="53"/>
       <c r="B17" s="4" t="s">
         <v>44</v>
       </c>
@@ -7229,7 +7226,7 @@
       <c r="S17" s="9"/>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="52"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="4" t="s">
         <v>44</v>
       </c>
@@ -7260,7 +7257,7 @@
       <c r="S18" s="9"/>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="52"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="4" t="s">
         <v>44</v>
       </c>
@@ -7291,7 +7288,7 @@
       <c r="S19" s="9"/>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="52"/>
+      <c r="A20" s="53"/>
       <c r="B20" s="4" t="s">
         <v>44</v>
       </c>
@@ -7322,7 +7319,7 @@
       <c r="S20" s="9"/>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="52"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="4" t="s">
         <v>44</v>
       </c>
@@ -7353,7 +7350,7 @@
       <c r="S21" s="9"/>
     </row>
     <row r="22" spans="1:19">
-      <c r="A22" s="52"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="4" t="s">
         <v>44</v>
       </c>
@@ -7384,7 +7381,7 @@
       <c r="S22" s="9"/>
     </row>
     <row r="23" spans="1:19">
-      <c r="A23" s="52"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="4" t="s">
         <v>44</v>
       </c>
@@ -7415,7 +7412,7 @@
       <c r="S23" s="9"/>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="52"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="4" t="s">
         <v>44</v>
       </c>
@@ -7446,7 +7443,7 @@
       <c r="S24" s="9"/>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="52"/>
+      <c r="A25" s="53"/>
       <c r="B25" s="4" t="s">
         <v>44</v>
       </c>
@@ -7477,7 +7474,7 @@
       <c r="S25" s="9"/>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="52"/>
+      <c r="A26" s="53"/>
       <c r="B26" s="4" t="s">
         <v>44</v>
       </c>
@@ -7508,7 +7505,7 @@
       <c r="S26" s="9"/>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="52"/>
+      <c r="A27" s="53"/>
       <c r="B27" s="4" t="s">
         <v>44</v>
       </c>
@@ -7539,7 +7536,7 @@
       <c r="S27" s="9"/>
     </row>
     <row r="28" spans="1:19">
-      <c r="A28" s="52"/>
+      <c r="A28" s="53"/>
       <c r="B28" s="4" t="s">
         <v>44</v>
       </c>
@@ -7570,7 +7567,7 @@
       <c r="S28" s="9"/>
     </row>
     <row r="29" spans="1:19">
-      <c r="A29" s="52"/>
+      <c r="A29" s="53"/>
       <c r="B29" s="4" t="s">
         <v>44</v>
       </c>
@@ -7601,7 +7598,7 @@
       <c r="S29" s="9"/>
     </row>
     <row r="30" spans="1:19">
-      <c r="A30" s="52"/>
+      <c r="A30" s="53"/>
       <c r="B30" s="4" t="s">
         <v>44</v>
       </c>
@@ -7632,7 +7629,7 @@
       <c r="S30" s="9"/>
     </row>
     <row r="31" spans="1:19">
-      <c r="A31" s="52"/>
+      <c r="A31" s="53"/>
       <c r="B31" s="4" t="s">
         <v>44</v>
       </c>
@@ -7663,7 +7660,7 @@
       <c r="S31" s="9"/>
     </row>
     <row r="32" spans="1:19">
-      <c r="A32" s="52"/>
+      <c r="A32" s="53"/>
       <c r="B32" s="4" t="s">
         <v>44</v>
       </c>
@@ -7694,7 +7691,7 @@
       <c r="S32" s="9"/>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="52"/>
+      <c r="A33" s="53"/>
       <c r="B33" s="4" t="s">
         <v>44</v>
       </c>
@@ -7725,7 +7722,7 @@
       <c r="S33" s="9"/>
     </row>
     <row r="34" spans="1:19">
-      <c r="A34" s="52"/>
+      <c r="A34" s="53"/>
       <c r="B34" s="4" t="s">
         <v>44</v>
       </c>
@@ -7756,7 +7753,7 @@
       <c r="S34" s="9"/>
     </row>
     <row r="35" spans="1:19">
-      <c r="A35" s="52"/>
+      <c r="A35" s="53"/>
       <c r="B35" s="4" t="s">
         <v>44</v>
       </c>
@@ -7787,7 +7784,7 @@
       <c r="S35" s="9"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="52"/>
+      <c r="A36" s="53"/>
       <c r="B36" s="4" t="s">
         <v>44</v>
       </c>
@@ -7818,7 +7815,7 @@
       <c r="S36" s="9"/>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="52"/>
+      <c r="A37" s="53"/>
       <c r="B37" s="4" t="s">
         <v>44</v>
       </c>
@@ -7849,7 +7846,7 @@
       <c r="S37" s="9"/>
     </row>
     <row r="38" spans="1:19">
-      <c r="A38" s="52"/>
+      <c r="A38" s="53"/>
       <c r="B38" s="4" t="s">
         <v>44</v>
       </c>
@@ -7880,7 +7877,7 @@
       <c r="S38" s="9"/>
     </row>
     <row r="39" spans="1:19">
-      <c r="A39" s="52"/>
+      <c r="A39" s="53"/>
       <c r="B39" s="4" t="s">
         <v>44</v>
       </c>
@@ -7911,7 +7908,7 @@
       <c r="S39" s="9"/>
     </row>
     <row r="40" spans="1:19">
-      <c r="A40" s="52"/>
+      <c r="A40" s="53"/>
       <c r="B40" s="4" t="s">
         <v>44</v>
       </c>
@@ -7942,7 +7939,7 @@
       <c r="S40" s="9"/>
     </row>
     <row r="41" spans="1:19">
-      <c r="A41" s="52"/>
+      <c r="A41" s="53"/>
       <c r="B41" s="4" t="s">
         <v>44</v>
       </c>
@@ -7973,7 +7970,7 @@
       <c r="S41" s="9"/>
     </row>
     <row r="42" spans="1:19">
-      <c r="A42" s="52"/>
+      <c r="A42" s="53"/>
       <c r="B42" s="4" t="s">
         <v>44</v>
       </c>
@@ -8004,7 +8001,7 @@
       <c r="S42" s="9"/>
     </row>
     <row r="43" spans="1:19">
-      <c r="A43" s="53"/>
+      <c r="A43" s="54"/>
       <c r="B43" s="4" t="s">
         <v>44</v>
       </c>
@@ -8077,48 +8074,48 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E74756A6-0373-4E3B-A4AF-75C0533D8867}">
   <dimension ref="A1:AC42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.875" customWidth="1"/>
     <col min="4" max="4" width="45" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" customWidth="1"/>
-    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="14" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="29" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15.5" customWidth="1"/>
     <col min="24" max="24" width="22.5" customWidth="1"/>
     <col min="25" max="25" width="15.5" customWidth="1"/>
     <col min="26" max="26" width="22" customWidth="1"/>
-    <col min="27" max="27" width="13.33203125" customWidth="1"/>
+    <col min="27" max="27" width="13.375" customWidth="1"/>
     <col min="28" max="28" width="13" customWidth="1"/>
-    <col min="29" max="29" width="11.33203125" customWidth="1"/>
+    <col min="29" max="29" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="61"/>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
       <c r="H1" s="18"/>
@@ -8139,13 +8136,13 @@
       <c r="A2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="64" t="str">
+      <c r="B2" s="65" t="str">
         <f>"https://rde.nims.go.jp/rde/dataset-templates/"&amp;説明!B3&amp;"/invoice.schema.json"</f>
         <v>https://rde.nims.go.jp/rde/dataset-templates/RDEDatasetTemplateSheet_rde_template_tools_sample/invoice.schema.json</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="67"/>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
       <c r="H2" s="18"/>
@@ -8166,13 +8163,13 @@
       <c r="A3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="61" t="str">
+      <c r="B3" s="62" t="str">
         <f>説明!B4&amp;": 送状定義"</f>
         <v>rde_template_tools用サンプル: 送状定義</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="64"/>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
       <c r="H3" s="18"/>
@@ -8390,10 +8387,10 @@
       </c>
     </row>
     <row r="7" spans="1:29">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="55" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -8413,7 +8410,7 @@
         <v>1493</v>
       </c>
       <c r="I7" s="50" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="J7" s="19"/>
       <c r="K7" s="23"/>
@@ -8450,8 +8447,8 @@
       <c r="AC7" s="19"/>
     </row>
     <row r="8" spans="1:29">
-      <c r="A8" s="54"/>
-      <c r="B8" s="54"/>
+      <c r="A8" s="55"/>
+      <c r="B8" s="55"/>
       <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
@@ -8460,9 +8457,7 @@
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
       <c r="H8" s="19"/>
-      <c r="I8" s="19" t="s">
-        <v>1494</v>
-      </c>
+      <c r="I8" s="51"/>
       <c r="J8" s="19"/>
       <c r="K8" s="23"/>
       <c r="L8" s="8"/>
@@ -8496,8 +8491,8 @@
       <c r="AC8" s="19"/>
     </row>
     <row r="9" spans="1:29">
-      <c r="A9" s="54"/>
-      <c r="B9" s="54"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="4" t="s">
         <v>44</v>
       </c>
@@ -8540,8 +8535,8 @@
       <c r="AC9" s="19"/>
     </row>
     <row r="10" spans="1:29">
-      <c r="A10" s="54"/>
-      <c r="B10" s="54"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="55"/>
       <c r="C10" s="4" t="s">
         <v>44</v>
       </c>
@@ -8584,8 +8579,8 @@
       <c r="AC10" s="19"/>
     </row>
     <row r="11" spans="1:29">
-      <c r="A11" s="54"/>
-      <c r="B11" s="54"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="55"/>
       <c r="C11" s="4" t="s">
         <v>44</v>
       </c>
@@ -8628,8 +8623,8 @@
       <c r="AC11" s="19"/>
     </row>
     <row r="12" spans="1:29">
-      <c r="A12" s="54"/>
-      <c r="B12" s="54"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="4" t="s">
         <v>44</v>
       </c>
@@ -8672,8 +8667,8 @@
       <c r="AC12" s="19"/>
     </row>
     <row r="13" spans="1:29">
-      <c r="A13" s="54"/>
-      <c r="B13" s="54"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="4" t="s">
         <v>44</v>
       </c>
@@ -8716,8 +8711,8 @@
       <c r="AC13" s="19"/>
     </row>
     <row r="14" spans="1:29">
-      <c r="A14" s="54"/>
-      <c r="B14" s="54"/>
+      <c r="A14" s="55"/>
+      <c r="B14" s="55"/>
       <c r="C14" s="4" t="s">
         <v>44</v>
       </c>
@@ -8760,8 +8755,8 @@
       <c r="AC14" s="1"/>
     </row>
     <row r="15" spans="1:29">
-      <c r="A15" s="54"/>
-      <c r="B15" s="54"/>
+      <c r="A15" s="55"/>
+      <c r="B15" s="55"/>
       <c r="C15" s="4" t="s">
         <v>44</v>
       </c>
@@ -8804,8 +8799,8 @@
       <c r="AC15" s="1"/>
     </row>
     <row r="16" spans="1:29">
-      <c r="A16" s="54"/>
-      <c r="B16" s="54"/>
+      <c r="A16" s="55"/>
+      <c r="B16" s="55"/>
       <c r="C16" s="4" t="s">
         <v>44</v>
       </c>
@@ -8848,8 +8843,8 @@
       <c r="AC16" s="1"/>
     </row>
     <row r="17" spans="1:29">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="55"/>
       <c r="C17" s="4" t="s">
         <v>44</v>
       </c>
@@ -8892,10 +8887,10 @@
       <c r="AC17" s="1"/>
     </row>
     <row r="18" spans="1:29">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="56" t="s">
         <v>1379</v>
       </c>
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="55" t="s">
         <v>79</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -8935,8 +8930,8 @@
       <c r="AC18" s="28"/>
     </row>
     <row r="19" spans="1:29">
-      <c r="A19" s="56"/>
-      <c r="B19" s="54"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="55"/>
       <c r="C19" s="4" t="s">
         <v>44</v>
       </c>
@@ -8974,8 +8969,8 @@
       <c r="AC19" s="28"/>
     </row>
     <row r="20" spans="1:29">
-      <c r="A20" s="56"/>
-      <c r="B20" s="54"/>
+      <c r="A20" s="57"/>
+      <c r="B20" s="55"/>
       <c r="C20" s="4" t="s">
         <v>44</v>
       </c>
@@ -9013,8 +9008,8 @@
       <c r="AC20" s="28"/>
     </row>
     <row r="21" spans="1:29">
-      <c r="A21" s="56"/>
-      <c r="B21" s="54"/>
+      <c r="A21" s="57"/>
+      <c r="B21" s="55"/>
       <c r="C21" s="4" t="s">
         <v>44</v>
       </c>
@@ -9052,8 +9047,8 @@
       <c r="AC21" s="28"/>
     </row>
     <row r="22" spans="1:29">
-      <c r="A22" s="56"/>
-      <c r="B22" s="54"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="55"/>
       <c r="C22" s="4" t="s">
         <v>44</v>
       </c>
@@ -9091,8 +9086,8 @@
       <c r="AC22" s="28"/>
     </row>
     <row r="23" spans="1:29">
-      <c r="A23" s="56"/>
-      <c r="B23" s="54"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="55"/>
       <c r="C23" s="4" t="s">
         <v>44</v>
       </c>
@@ -9130,8 +9125,8 @@
       <c r="AC23" s="28"/>
     </row>
     <row r="24" spans="1:29">
-      <c r="A24" s="57"/>
-      <c r="B24" s="54"/>
+      <c r="A24" s="58"/>
+      <c r="B24" s="55"/>
       <c r="C24" s="4" t="s">
         <v>44</v>
       </c>
@@ -9169,10 +9164,10 @@
       <c r="AC24" s="28"/>
     </row>
     <row r="25" spans="1:29">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="56" t="s">
         <v>1380</v>
       </c>
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="55" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -9223,8 +9218,8 @@
       <c r="AC25" s="28"/>
     </row>
     <row r="26" spans="1:29">
-      <c r="A26" s="56"/>
-      <c r="B26" s="54"/>
+      <c r="A26" s="57"/>
+      <c r="B26" s="55"/>
       <c r="C26" s="4" t="s">
         <v>44</v>
       </c>
@@ -9271,8 +9266,8 @@
       <c r="AC26" s="28"/>
     </row>
     <row r="27" spans="1:29">
-      <c r="A27" s="56"/>
-      <c r="B27" s="54"/>
+      <c r="A27" s="57"/>
+      <c r="B27" s="55"/>
       <c r="C27" s="4" t="s">
         <v>44</v>
       </c>
@@ -9319,8 +9314,8 @@
       <c r="AC27" s="28"/>
     </row>
     <row r="28" spans="1:29">
-      <c r="A28" s="56"/>
-      <c r="B28" s="54"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="55"/>
       <c r="C28" s="4" t="s">
         <v>44</v>
       </c>
@@ -9367,8 +9362,8 @@
       <c r="AC28" s="28"/>
     </row>
     <row r="29" spans="1:29">
-      <c r="A29" s="56"/>
-      <c r="B29" s="54"/>
+      <c r="A29" s="57"/>
+      <c r="B29" s="55"/>
       <c r="C29" s="4" t="s">
         <v>44</v>
       </c>
@@ -9415,8 +9410,8 @@
       <c r="AC29" s="28"/>
     </row>
     <row r="30" spans="1:29">
-      <c r="A30" s="56"/>
-      <c r="B30" s="54"/>
+      <c r="A30" s="57"/>
+      <c r="B30" s="55"/>
       <c r="C30" s="4" t="s">
         <v>44</v>
       </c>
@@ -9463,8 +9458,8 @@
       <c r="AC30" s="28"/>
     </row>
     <row r="31" spans="1:29">
-      <c r="A31" s="56"/>
-      <c r="B31" s="54"/>
+      <c r="A31" s="57"/>
+      <c r="B31" s="55"/>
       <c r="C31" s="4" t="s">
         <v>44</v>
       </c>
@@ -9511,8 +9506,8 @@
       <c r="AC31" s="28"/>
     </row>
     <row r="32" spans="1:29">
-      <c r="A32" s="56"/>
-      <c r="B32" s="54"/>
+      <c r="A32" s="57"/>
+      <c r="B32" s="55"/>
       <c r="C32" s="4" t="s">
         <v>44</v>
       </c>
@@ -9559,8 +9554,8 @@
       <c r="AC32" s="28"/>
     </row>
     <row r="33" spans="1:29">
-      <c r="A33" s="57"/>
-      <c r="B33" s="54"/>
+      <c r="A33" s="58"/>
+      <c r="B33" s="55"/>
       <c r="C33" s="4" t="s">
         <v>44</v>
       </c>
@@ -9607,10 +9602,10 @@
       <c r="AC33" s="28"/>
     </row>
     <row r="34" spans="1:29">
-      <c r="A34" s="55" t="s">
+      <c r="A34" s="56" t="s">
         <v>1381</v>
       </c>
-      <c r="B34" s="54" t="s">
+      <c r="B34" s="55" t="s">
         <v>41</v>
       </c>
       <c r="C34" s="4" t="s">
@@ -9659,8 +9654,8 @@
       <c r="AC34" s="28"/>
     </row>
     <row r="35" spans="1:29">
-      <c r="A35" s="56"/>
-      <c r="B35" s="54"/>
+      <c r="A35" s="57"/>
+      <c r="B35" s="55"/>
       <c r="C35" s="4" t="s">
         <v>44</v>
       </c>
@@ -9707,8 +9702,8 @@
       <c r="AC35" s="28"/>
     </row>
     <row r="36" spans="1:29">
-      <c r="A36" s="56"/>
-      <c r="B36" s="54"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="55"/>
       <c r="C36" s="4" t="s">
         <v>44</v>
       </c>
@@ -9755,8 +9750,8 @@
       <c r="AC36" s="28"/>
     </row>
     <row r="37" spans="1:29">
-      <c r="A37" s="56"/>
-      <c r="B37" s="54"/>
+      <c r="A37" s="57"/>
+      <c r="B37" s="55"/>
       <c r="C37" s="4" t="s">
         <v>44</v>
       </c>
@@ -9803,8 +9798,8 @@
       <c r="AC37" s="28"/>
     </row>
     <row r="38" spans="1:29">
-      <c r="A38" s="56"/>
-      <c r="B38" s="54"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="55"/>
       <c r="C38" s="4" t="s">
         <v>44</v>
       </c>
@@ -9851,8 +9846,8 @@
       <c r="AC38" s="28"/>
     </row>
     <row r="39" spans="1:29">
-      <c r="A39" s="56"/>
-      <c r="B39" s="54"/>
+      <c r="A39" s="57"/>
+      <c r="B39" s="55"/>
       <c r="C39" s="4" t="s">
         <v>44</v>
       </c>
@@ -9899,8 +9894,8 @@
       <c r="AC39" s="28"/>
     </row>
     <row r="40" spans="1:29">
-      <c r="A40" s="56"/>
-      <c r="B40" s="54"/>
+      <c r="A40" s="57"/>
+      <c r="B40" s="55"/>
       <c r="C40" s="4" t="s">
         <v>44</v>
       </c>
@@ -9947,8 +9942,8 @@
       <c r="AC40" s="28"/>
     </row>
     <row r="41" spans="1:29">
-      <c r="A41" s="56"/>
-      <c r="B41" s="54"/>
+      <c r="A41" s="57"/>
+      <c r="B41" s="55"/>
       <c r="C41" s="4" t="s">
         <v>44</v>
       </c>
@@ -9995,8 +9990,8 @@
       <c r="AC41" s="28"/>
     </row>
     <row r="42" spans="1:29">
-      <c r="A42" s="57"/>
-      <c r="B42" s="54"/>
+      <c r="A42" s="58"/>
+      <c r="B42" s="55"/>
       <c r="C42" s="4" t="s">
         <v>44</v>
       </c>
@@ -10152,38 +10147,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D22F99-B59B-4D69-9661-508AD2B5EFA1}">
   <dimension ref="A1:Z18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="5" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="15.6640625" customWidth="1"/>
-    <col min="8" max="9" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.6640625" customWidth="1"/>
+    <col min="3" max="5" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="9" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.625" customWidth="1"/>
     <col min="17" max="19" width="29" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="22.5" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="15.5" hidden="1" customWidth="1"/>
     <col min="22" max="23" width="22" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="13" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="14.1640625" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="14.125" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="11.375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="70" t="s">
+      <c r="B1" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
       <c r="H1" s="18"/>
@@ -10208,13 +10203,13 @@
       <c r="A2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="71" t="str">
+      <c r="B2" s="72" t="str">
         <f>"https://rde.nims.go.jp/rde/dataset-templates/"&amp;説明!B3&amp;"/catalog.schema.json"</f>
         <v>https://rde.nims.go.jp/rde/dataset-templates/RDEDatasetTemplateSheet_rde_template_tools_sample/catalog.schema.json</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
       <c r="F2" s="35"/>
       <c r="G2" s="33"/>
       <c r="H2" s="18"/>
@@ -10239,13 +10234,13 @@
       <c r="A3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="72" t="str">
+      <c r="B3" s="73" t="str">
         <f>説明!B4&amp;": データカタログ定義"</f>
         <v>rde_template_tools用サンプル: データカタログ定義</v>
       </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
       <c r="F3" s="18"/>
       <c r="G3" s="34"/>
       <c r="H3" s="18"/>
@@ -10270,13 +10265,13 @@
       <c r="A4" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="71" t="str">
+      <c r="B4" s="72" t="str">
         <f>説明!B1&amp;":データカタログ定義"</f>
         <v>RDEDatasetTemplateSheet_rde_template_tools_sample:データカタログ定義</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
       <c r="F4" s="35"/>
       <c r="G4" s="33"/>
       <c r="H4" s="18"/>
@@ -10301,13 +10296,13 @@
       <c r="A5" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="71" t="str">
+      <c r="B5" s="72" t="str">
         <f>説明!B2&amp;":data catalog format"</f>
         <v>RDEDatasetTemplateSheet_rde_template_tools_sample:data catalog format</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
       <c r="F5" s="35"/>
       <c r="G5" s="33"/>
       <c r="H5" s="18"/>
@@ -10515,7 +10510,7 @@
       </c>
     </row>
     <row r="9" spans="1:26">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="68" t="s">
         <v>1428</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -10568,7 +10563,7 @@
       <c r="Z9" s="19"/>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="68"/>
+      <c r="A10" s="69"/>
       <c r="B10" s="4" t="s">
         <v>1402</v>
       </c>
@@ -10619,7 +10614,7 @@
       <c r="Z10" s="19"/>
     </row>
     <row r="11" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A11" s="68"/>
+      <c r="A11" s="69"/>
       <c r="B11" s="4" t="s">
         <v>1402</v>
       </c>
@@ -10672,7 +10667,7 @@
       <c r="Z11" s="19"/>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="68"/>
+      <c r="A12" s="69"/>
       <c r="B12" s="4" t="s">
         <v>1402</v>
       </c>
@@ -10725,7 +10720,7 @@
       <c r="Z12" s="19"/>
     </row>
     <row r="13" spans="1:26">
-      <c r="A13" s="68"/>
+      <c r="A13" s="69"/>
       <c r="B13" s="4" t="s">
         <v>1402</v>
       </c>
@@ -10778,7 +10773,7 @@
       <c r="Z13" s="19"/>
     </row>
     <row r="14" spans="1:26">
-      <c r="A14" s="68"/>
+      <c r="A14" s="69"/>
       <c r="B14" s="4" t="s">
         <v>1402</v>
       </c>
@@ -10831,7 +10826,7 @@
       <c r="Z14" s="19"/>
     </row>
     <row r="15" spans="1:26">
-      <c r="A15" s="68"/>
+      <c r="A15" s="69"/>
       <c r="B15" s="4" t="s">
         <v>1402</v>
       </c>
@@ -10884,7 +10879,7 @@
       <c r="Z15" s="19"/>
     </row>
     <row r="16" spans="1:26">
-      <c r="A16" s="68"/>
+      <c r="A16" s="69"/>
       <c r="B16" s="4" t="s">
         <v>1402</v>
       </c>
@@ -10937,7 +10932,7 @@
       <c r="Z16" s="19"/>
     </row>
     <row r="17" spans="1:26">
-      <c r="A17" s="68"/>
+      <c r="A17" s="69"/>
       <c r="B17" s="4" t="s">
         <v>44</v>
       </c>
@@ -10982,7 +10977,7 @@
       <c r="Z17" s="19"/>
     </row>
     <row r="18" spans="1:26">
-      <c r="A18" s="69"/>
+      <c r="A18" s="70"/>
       <c r="B18" s="4" t="s">
         <v>44</v>
       </c>
@@ -11096,15 +11091,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9AC555-5AB8-4DD3-85B1-E048EC06BBB1}">
   <dimension ref="A1:G376"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="40.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.1640625" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" customWidth="1"/>
-    <col min="5" max="5" width="25.6640625" customWidth="1"/>
-    <col min="6" max="6" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.125" customWidth="1"/>
+    <col min="4" max="4" width="29.625" customWidth="1"/>
+    <col min="5" max="5" width="25.625" customWidth="1"/>
+    <col min="6" max="6" width="40.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -18376,16 +18371,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB8C9AE-9632-43A1-8EDC-D56208074D48}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="50.33203125" customWidth="1"/>
-    <col min="8" max="8" width="40.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="50.375" customWidth="1"/>
+    <col min="8" max="8" width="40.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -19191,7 +19186,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0C0B86-4875-43DF-B759-388074FE35CB}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="40.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
@@ -19295,20 +19290,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F59ACC8B-6394-4DBA-8ADA-86BF5518B95C}">
   <dimension ref="A1:M36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="40.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="50.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="40.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="40.83203125" customWidth="1"/>
+    <col min="8" max="8" width="42.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="50.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40.875" customWidth="1"/>
     <col min="13" max="13" width="41.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
